--- a/data/trans_dic/P1418-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1418-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,65</t>
+          <t>2,09; 6,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,62</t>
+          <t>1,61; 5,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,19</t>
+          <t>0,82; 4,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,5</t>
+          <t>0,74; 3,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,84</t>
+          <t>5,78; 13,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,68</t>
+          <t>5,51; 12,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 13,88</t>
+          <t>7,01; 13,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,47</t>
+          <t>1,52; 4,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,75</t>
+          <t>4,53; 8,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,45</t>
+          <t>4,06; 8,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,15</t>
+          <t>4,09; 8,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,36</t>
+          <t>1,45; 3,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,67</t>
+          <t>4,01; 8,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,75</t>
+          <t>1,44; 4,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,25</t>
+          <t>0,84; 3,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,91</t>
+          <t>1,24; 3,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 17,02</t>
+          <t>10,5; 16,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,56</t>
+          <t>4,78; 9,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,26</t>
+          <t>3,06; 7,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,6</t>
+          <t>4,32; 7,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 12,09</t>
+          <t>8,0; 11,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,38</t>
+          <t>3,63; 6,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,61</t>
+          <t>2,2; 4,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,24</t>
+          <t>3,11; 5,24</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,24</t>
+          <t>1,98; 5,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,07</t>
+          <t>1,9; 6,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,7</t>
+          <t>1,76; 5,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,74</t>
+          <t>3,96; 8,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,44</t>
+          <t>4,69; 10,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,01</t>
+          <t>4,31; 10,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,81</t>
+          <t>2,3; 6,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,36</t>
+          <t>6,19; 10,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,21</t>
+          <t>3,91; 7,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,39</t>
+          <t>3,6; 7,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,46</t>
+          <t>2,46; 5,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,78</t>
+          <t>5,63; 8,84</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,4</t>
+          <t>1,82; 5,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,7</t>
+          <t>2,23; 6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,0</t>
+          <t>1,04; 4,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,99</t>
+          <t>2,31; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,85</t>
+          <t>5,46; 10,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,1; 17,89</t>
+          <t>10,71; 18,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,75</t>
+          <t>2,88; 7,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,4</t>
+          <t>4,02; 7,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,65</t>
+          <t>4,28; 7,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,77</t>
+          <t>7,35; 11,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,13</t>
+          <t>2,38; 5,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,92</t>
+          <t>3,55; 6,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,56</t>
+          <t>2,87; 9,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,65</t>
+          <t>2,18; 8,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,47</t>
+          <t>1,49; 5,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,61</t>
+          <t>7,13; 15,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,77; 20,43</t>
+          <t>11,0; 20,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,46</t>
+          <t>3,48; 10,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,87</t>
+          <t>8,2; 13,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,86</t>
+          <t>5,54; 10,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 13,41</t>
+          <t>7,63; 13,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,51</t>
+          <t>1,93; 5,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,04</t>
+          <t>5,46; 8,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,25</t>
+          <t>1,82; 6,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,87</t>
+          <t>1,87; 6,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,79</t>
+          <t>1,81; 6,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,01</t>
+          <t>6,14; 10,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 14,42</t>
+          <t>7,11; 14,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,55; 13,68</t>
+          <t>6,56; 13,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,39</t>
+          <t>3,74; 10,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,75; 18,1</t>
+          <t>12,06; 18,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,43</t>
+          <t>4,91; 9,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,02</t>
+          <t>4,69; 9,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,25</t>
+          <t>3,25; 6,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,59; 13,52</t>
+          <t>9,6; 13,39</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,99</t>
+          <t>3,22; 6,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,06</t>
+          <t>2,76; 6,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,97</t>
+          <t>1,96; 4,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 9,12</t>
+          <t>4,74; 8,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,38</t>
+          <t>7,06; 11,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,26</t>
+          <t>9,07; 14,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,95</t>
+          <t>8,04; 13,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 17,49</t>
+          <t>14,14; 18,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,64</t>
+          <t>5,66; 8,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,54</t>
+          <t>6,38; 9,59</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,51</t>
+          <t>5,57; 8,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 12,32</t>
+          <t>10,05; 13,18</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,29</t>
+          <t>6,93; 11,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,37</t>
+          <t>0,69; 2,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,57</t>
+          <t>1,26; 3,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,65</t>
+          <t>2,01; 4,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,27; 13,79</t>
+          <t>9,19; 14,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,28; 10,28</t>
+          <t>6,49; 10,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,87</t>
+          <t>5,84; 9,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,14</t>
+          <t>4,75; 7,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,69</t>
+          <t>8,7; 11,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,05</t>
+          <t>3,84; 6,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,24</t>
+          <t>3,96; 6,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,74</t>
+          <t>3,71; 5,58</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,28</t>
+          <t>4,76; 6,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 3,76</t>
+          <t>2,51; 3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,94</t>
+          <t>1,9; 3,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 4,73</t>
+          <t>3,63; 4,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,14; 11,28</t>
+          <t>9,16; 11,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,8</t>
+          <t>8,8; 10,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,16</t>
+          <t>6,28; 8,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,31</t>
+          <t>8,08; 9,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,48</t>
+          <t>7,14; 8,49</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,08</t>
+          <t>5,91; 7,12</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,38</t>
+          <t>4,24; 5,39</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,8</t>
+          <t>6,11; 7,13</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13002</t>
+          <t>13667</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6342; 18143</t>
+          <t>5698; 18299</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4658; 16553</t>
+          <t>4744; 16175</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2385; 12322</t>
+          <t>2414; 12502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1973; 10900</t>
+          <t>2346; 11220</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14303; 33501</t>
+          <t>15086; 34077</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15558; 36433</t>
+          <t>15840; 35408</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19861; 40076</t>
+          <t>20230; 40398</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4798; 12950</t>
+          <t>4784; 12721</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23500; 46689</t>
+          <t>24188; 46368</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24007; 49179</t>
+          <t>23626; 46957</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24764; 47498</t>
+          <t>23848; 47115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8326; 20200</t>
+          <t>9182; 20980</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41734</t>
+          <t>43402</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20271; 42741</t>
+          <t>19749; 42435</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7217; 23998</t>
+          <t>7258; 24858</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4142; 16317</t>
+          <t>4246; 15873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6285; 20220</t>
+          <t>6552; 20709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54239; 85795</t>
+          <t>52893; 85429</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24988; 50065</t>
+          <t>25038; 51402</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15579; 37992</t>
+          <t>16007; 37406</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22338; 38991</t>
+          <t>23540; 41652</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82104; 120554</t>
+          <t>79789; 118931</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36419; 65665</t>
+          <t>37415; 66649</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22655; 47296</t>
+          <t>22597; 47828</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31552; 54000</t>
+          <t>33386; 56228</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>47807</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6347; 19893</t>
+          <t>6318; 18935</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6144; 19658</t>
+          <t>6153; 20256</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5882; 18146</t>
+          <t>5620; 17516</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13433; 27607</t>
+          <t>12527; 26716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16116; 35014</t>
+          <t>15719; 35468</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14709; 34138</t>
+          <t>14690; 34618</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7320; 22906</t>
+          <t>7733; 22150</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21676; 36167</t>
+          <t>22054; 38321</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25091; 47160</t>
+          <t>25597; 46858</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24242; 49150</t>
+          <t>23925; 47236</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16521; 35774</t>
+          <t>16087; 35415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37462; 58431</t>
+          <t>37838; 59413</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34140</t>
+          <t>38180</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6423; 19354</t>
+          <t>6538; 20066</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8571; 25072</t>
+          <t>8332; 24679</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3566; 14798</t>
+          <t>3840; 15056</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7368; 21856</t>
+          <t>8602; 24462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20564; 40289</t>
+          <t>20265; 40698</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43186; 69588</t>
+          <t>41645; 71152</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11070; 30022</t>
+          <t>11170; 29708</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13003; 30452</t>
+          <t>16950; 30310</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30349; 55858</t>
+          <t>31227; 54228</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54586; 89835</t>
+          <t>56087; 89889</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17049; 38877</t>
+          <t>18042; 39712</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24319; 46691</t>
+          <t>28221; 50265</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>29832</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5953; 19440</t>
+          <t>5841; 18355</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4572; 18400</t>
+          <t>4642; 18524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5055</t>
+          <t>0; 5490</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2987; 9777</t>
+          <t>3069; 10665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13984; 32421</t>
+          <t>14801; 31786</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23648; 44871</t>
+          <t>24165; 45737</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7705; 22861</t>
+          <t>7616; 22578</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17561; 28845</t>
+          <t>18582; 30301</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22932; 44620</t>
+          <t>22767; 44981</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32445; 57949</t>
+          <t>32989; 57015</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7575; 23693</t>
+          <t>8305; 24355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21567; 34966</t>
+          <t>23597; 38198</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>61167</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4973; 16915</t>
+          <t>4920; 17119</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4242; 16073</t>
+          <t>5122; 16920</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4162; 15232</t>
+          <t>4774; 16556</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16585; 29674</t>
+          <t>16630; 29476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20258; 40097</t>
+          <t>19778; 40930</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18215; 38039</t>
+          <t>18251; 38346</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10450; 28380</t>
+          <t>10212; 27458</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30122; 46408</t>
+          <t>31720; 47848</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27997; 51771</t>
+          <t>26957; 50797</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26206; 49802</t>
+          <t>25897; 49810</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17203; 38883</t>
+          <t>17428; 37091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50456; 71138</t>
+          <t>51227; 71477</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40227</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>106951</t>
+          <t>124276</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>147177</t>
+          <t>169845</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20835; 43015</t>
+          <t>19816; 43004</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17994; 40157</t>
+          <t>18287; 41600</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13476; 32641</t>
+          <t>12894; 32218</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29155; 56576</t>
+          <t>33897; 62186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44024; 72644</t>
+          <t>45079; 72215</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>63272; 98932</t>
+          <t>62934; 99026</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55351; 89523</t>
+          <t>55553; 90005</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43646; 148044</t>
+          <t>108584; 145201</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70482; 108335</t>
+          <t>70930; 107805</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86721; 129405</t>
+          <t>86495; 130047</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76579; 114649</t>
+          <t>75081; 116673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89593; 180666</t>
+          <t>148974; 195462</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>24344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>48308</t>
+          <t>50245</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>70004</t>
+          <t>74589</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>52056; 83963</t>
+          <t>51547; 83012</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5325; 18496</t>
+          <t>5339; 19571</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9694; 27759</t>
+          <t>9802; 27421</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9743; 33884</t>
+          <t>16014; 34763</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>72593; 108058</t>
+          <t>72002; 110619</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51563; 84436</t>
+          <t>53284; 86739</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49534; 81531</t>
+          <t>48225; 80996</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>37402; 65347</t>
+          <t>39438; 62721</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>131317; 178508</t>
+          <t>132832; 180526</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>61355; 96911</t>
+          <t>61387; 97152</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62043; 100082</t>
+          <t>63573; 102838</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>44842; 94301</t>
+          <t>60441; 90769</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138907</t>
+          <t>149565</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>302680</t>
+          <t>328924</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>441588</t>
+          <t>478489</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>154201; 205646</t>
+          <t>156040; 206738</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>88191; 128787</t>
+          <t>86064; 129575</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64345; 99877</t>
+          <t>64449; 101690</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109528; 163291</t>
+          <t>127983; 172386</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>308880; 381226</t>
+          <t>309379; 378888</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>309986; 383820</t>
+          <t>312931; 383193</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>223146; 289290</t>
+          <t>222423; 285859</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>251747; 340066</t>
+          <t>301096; 357002</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>482505; 564282</t>
+          <t>475182; 565293</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>413206; 494468</t>
+          <t>412841; 497025</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>301375; 373029</t>
+          <t>294386; 373711</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>379743; 483252</t>
+          <t>443396; 517126</t>
         </is>
       </c>
     </row>
